--- a/bio/player_bio.xlsx
+++ b/bio/player_bio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7881D9BD-5516-D64D-BA4A-39F700ACF160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA229ED-4556-1946-9EA8-C9039BF652D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -748,7 +748,7 @@
         <v>62</v>
       </c>
       <c r="H5" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/bio/player_bio.xlsx
+++ b/bio/player_bio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA229ED-4556-1946-9EA8-C9039BF652D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD31C46-4466-0341-BC45-66436C411209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,9 +207,6 @@
     <t>Feri</t>
   </si>
   <si>
-    <t>Gwen Stefani, Akon - The Sweet Escape</t>
-  </si>
-  <si>
     <t>Queens of the Stone Age - In My Head</t>
   </si>
   <si>
@@ -235,6 +232,9 @@
   </si>
   <si>
     <t>22g Winmau MvG Assault</t>
+  </si>
+  <si>
+    <t>JAY-Z, Rihanna, Kanye West - Run This Town</t>
   </si>
 </sst>
 </file>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="H4" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -745,7 +745,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H5" s="6">
         <v>13</v>
@@ -823,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H8" s="6">
         <v>2</v>
@@ -875,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H10" s="6">
         <v>1</v>
@@ -953,7 +953,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="6">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H14" s="6">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D15" s="3">
         <v>39597</v>
@@ -1013,13 +1013,13 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" s="13">
         <v>35682</v>
@@ -1031,7 +1031,7 @@
         <v>9</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H16" s="12">
         <v>7</v>

--- a/bio/player_bio.xlsx
+++ b/bio/player_bio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD31C46-4466-0341-BC45-66436C411209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF57CE6-0623-CA42-8311-822D94DD3E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="H4" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/bio/player_bio.xlsx
+++ b/bio/player_bio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF57CE6-0623-CA42-8311-822D94DD3E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E4218B-6053-7548-AD28-8F4064440B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,9 +111,6 @@
     <t>The President</t>
   </si>
   <si>
-    <t xml:space="preserve">Bellini - Samba de Janeiro </t>
-  </si>
-  <si>
     <t>Ármin Szücs</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t>The Killers - Mr. Brightside</t>
   </si>
   <si>
-    <t xml:space="preserve">Bee Gees - Stayin Alive </t>
-  </si>
-  <si>
     <t>Guli</t>
   </si>
   <si>
@@ -235,6 +229,12 @@
   </si>
   <si>
     <t>JAY-Z, Rihanna, Kanye West - Run This Town</t>
+  </si>
+  <si>
+    <t>Bee Gees - Stayin Alive</t>
+  </si>
+  <si>
+    <t>Bellini - Samba de Janeiro</t>
   </si>
 </sst>
 </file>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -641,10 +641,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -693,7 +693,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H3" s="6">
         <v>2</v>
@@ -719,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H4" s="6">
         <v>10</v>
@@ -730,7 +730,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
@@ -745,7 +745,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H5" s="6">
         <v>13</v>
@@ -756,10 +756,10 @@
         <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="3">
         <v>37068</v>
@@ -771,7 +771,7 @@
         <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6">
         <v>4</v>
@@ -785,7 +785,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="3">
         <v>36533</v>
@@ -797,7 +797,7 @@
         <v>9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H7" s="6">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="D8" s="3">
         <v>36485</v>
@@ -823,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H8" s="6">
         <v>2</v>
@@ -837,7 +837,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D9" s="3">
         <v>38962</v>
@@ -849,7 +849,7 @@
         <v>9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H9" s="6">
         <v>1</v>
@@ -857,13 +857,13 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D10" s="3">
         <v>35864</v>
@@ -875,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H10" s="6">
         <v>1</v>
@@ -883,13 +883,13 @@
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D11" s="3">
         <v>36439</v>
@@ -901,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H11" s="6">
         <v>0</v>
@@ -909,13 +909,13 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="D12" s="3">
         <v>36230</v>
@@ -927,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H12" s="6">
         <v>0</v>
@@ -935,13 +935,13 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" s="3">
         <v>37437</v>
@@ -953,7 +953,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H13" s="6">
         <v>0</v>
@@ -961,13 +961,13 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="3">
         <v>36552</v>
@@ -979,7 +979,7 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H14" s="6">
         <v>0</v>
@@ -987,13 +987,13 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" s="3">
         <v>39597</v>
@@ -1005,7 +1005,7 @@
         <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H15" s="6">
         <v>2</v>
@@ -1013,13 +1013,13 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" s="13">
         <v>35682</v>
@@ -1031,7 +1031,7 @@
         <v>9</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H16" s="12">
         <v>7</v>

--- a/bio/player_bio.xlsx
+++ b/bio/player_bio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E4218B-6053-7548-AD28-8F4064440B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6DB93C-71EF-AB44-9DA9-6A0657628E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
   <si>
     <t>Player</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>Bellini - Samba de Janeiro</t>
+  </si>
+  <si>
+    <t>26g Red Dragon Razor Edge</t>
   </si>
 </sst>
 </file>
@@ -722,7 +725,7 @@
         <v>44</v>
       </c>
       <c r="H4" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1005,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="H15" s="6">
         <v>2</v>

--- a/bio/player_bio.xlsx
+++ b/bio/player_bio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6DB93C-71EF-AB44-9DA9-6A0657628E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E06B319-9AFB-6445-AAA8-79B5A598EDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -611,7 +611,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
@@ -751,7 +751,7 @@
         <v>59</v>
       </c>
       <c r="H5" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1037,7 +1037,13 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>7</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H18">
+        <f>SUM(H2:H16)</f>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/bio/player_bio.xlsx
+++ b/bio/player_bio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E06B319-9AFB-6445-AAA8-79B5A598EDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F711A83F-4087-1A4A-B000-64773B6A72EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -611,7 +611,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
@@ -1037,13 +1037,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H18">
-        <f>SUM(H2:H16)</f>
-        <v>51</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
